--- a/data/processed/positivacao/2024-03_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2024-03_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26921,7 +26921,7 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr"/>
@@ -38273,7 +38273,7 @@
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr"/>
@@ -66567,7 +66567,7 @@
     <row r="2549">
       <c r="A2549" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2549" t="inlineStr"/>
@@ -68238,12 +68238,12 @@
       <c r="A2614" t="inlineStr"/>
       <c r="B2614" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 7 cliente(s), não positivou 85 cliente(s) - Total vendido: R$ 4.254,98
+          <t>Vendedor 1 - VENDEDOR 01: positivou 7 cliente(s), não positivou 85 cliente(s) - Total vendido: R$ 4.254,98
 Vendedor 18 - LOJA: positivou 237 cliente(s), não positivou 684 cliente(s) - Total vendido: R$ 129.649,39
-Vendedor 3 - FERNANDA: positivou 120 cliente(s), não positivou 316 cliente(s) - Total vendido: R$ 165.511,79
-Vendedor 4 - DANIELA: positivou 113 cliente(s), não positivou 536 cliente(s) - Total vendido: R$ 51.826,49
+Vendedor 3 - VENDEDOR 03: positivou 120 cliente(s), não positivou 316 cliente(s) - Total vendido: R$ 165.511,79
+Vendedor 4 - VENDEDOR 04: positivou 113 cliente(s), não positivou 536 cliente(s) - Total vendido: R$ 51.826,49
 Vendedor 5 - SITE: positivou 15 cliente(s), não positivou 423 cliente(s) - Total vendido: R$ 2.132,62
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2614" t="inlineStr"/>
